--- a/结果/认知层次分析报告.xlsx
+++ b/结果/认知层次分析报告.xlsx
@@ -434,7 +434,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>难度(平均得分率)</t>
+          <t>平均得分</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -461,13 +461,13 @@
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.743</v>
+        <v>7.433</v>
       </c>
       <c r="E2" t="n">
         <v>0.743</v>
       </c>
       <c r="F2" t="n">
-        <v>0.795</v>
+        <v>0.314</v>
       </c>
     </row>
     <row r="3">
@@ -483,13 +483,13 @@
         <v>40</v>
       </c>
       <c r="D3" t="n">
-        <v>0.746</v>
+        <v>29.844</v>
       </c>
       <c r="E3" t="n">
         <v>0.746</v>
       </c>
       <c r="F3" t="n">
-        <v>0.901</v>
+        <v>0.273</v>
       </c>
     </row>
     <row r="4">
@@ -505,13 +505,13 @@
         <v>50</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6879999999999999</v>
+        <v>34.417</v>
       </c>
       <c r="E4" t="n">
         <v>0.6879999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.949</v>
+        <v>0.302</v>
       </c>
     </row>
   </sheetData>
